--- a/Team-Data/2013-14/1-31-2013-14.xlsx
+++ b/Team-Data/2013-14/1-31-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,43 +728,43 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
         <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>0.533</v>
+        <v>0.523</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J2" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.372</v>
+        <v>0.37</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="P2" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="Q2" t="n">
         <v>0.783</v>
@@ -706,40 +773,40 @@
         <v>9.199999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T2" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U2" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="V2" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W2" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X2" t="n">
         <v>4.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.7</v>
+        <v>102.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE2" t="n">
         <v>13</v>
@@ -754,22 +821,22 @@
         <v>8</v>
       </c>
       <c r="AI2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL2" t="n">
         <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AO2" t="n">
         <v>18</v>
@@ -784,7 +851,7 @@
         <v>26</v>
       </c>
       <c r="AS2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>26</v>
@@ -796,13 +863,13 @@
         <v>22</v>
       </c>
       <c r="AW2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
@@ -814,7 +881,7 @@
         <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -933,10 +1000,10 @@
         <v>28</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ3" t="n">
         <v>15</v>
@@ -957,7 +1024,7 @@
         <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ3" t="n">
         <v>12</v>
@@ -975,7 +1042,7 @@
         <v>28</v>
       </c>
       <c r="AV3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW3" t="n">
         <v>23</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E4" t="n">
         <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" t="n">
-        <v>0.455</v>
+        <v>0.465</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1043,73 +1110,73 @@
         <v>35.3</v>
       </c>
       <c r="J4" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K4" t="n">
         <v>0.45</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M4" t="n">
         <v>21.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.371</v>
+        <v>0.369</v>
       </c>
       <c r="O4" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P4" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="R4" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S4" t="n">
-        <v>30.1</v>
+        <v>30.4</v>
       </c>
       <c r="T4" t="n">
-        <v>39.3</v>
+        <v>39.9</v>
       </c>
       <c r="U4" t="n">
         <v>20.8</v>
       </c>
       <c r="V4" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W4" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X4" t="n">
         <v>4.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z4" t="n">
         <v>22.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3</v>
+        <v>-2.5</v>
       </c>
       <c r="AD4" t="n">
         <v>30</v>
       </c>
       <c r="AE4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG4" t="n">
         <v>18</v>
@@ -1118,7 +1185,7 @@
         <v>7</v>
       </c>
       <c r="AI4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ4" t="n">
         <v>29</v>
@@ -1127,16 +1194,16 @@
         <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM4" t="n">
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AO4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP4" t="n">
         <v>9</v>
@@ -1148,10 +1215,10 @@
         <v>25</v>
       </c>
       <c r="AS4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU4" t="n">
         <v>18</v>
@@ -1160,10 +1227,10 @@
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AX4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY4" t="n">
         <v>8</v>
@@ -1172,13 +1239,13 @@
         <v>24</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -1207,43 +1274,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
         <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>0.438</v>
+        <v>0.426</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>35.3</v>
+        <v>35.1</v>
       </c>
       <c r="J5" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.434</v>
+        <v>0.432</v>
       </c>
       <c r="L5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O5" t="n">
         <v>18.3</v>
       </c>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q5" t="n">
         <v>0.73</v>
@@ -1252,13 +1319,13 @@
         <v>9.1</v>
       </c>
       <c r="S5" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="T5" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U5" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V5" t="n">
         <v>12.9</v>
@@ -1270,22 +1337,22 @@
         <v>5.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.8</v>
+        <v>-3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1300,10 +1367,10 @@
         <v>14</v>
       </c>
       <c r="AI5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1315,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO5" t="n">
         <v>10</v>
@@ -1327,16 +1394,16 @@
         <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AT5" t="n">
         <v>23</v>
       </c>
       <c r="AU5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AV5" t="n">
         <v>2</v>
@@ -1345,7 +1412,7 @@
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
         <v>22</v>
@@ -1354,13 +1421,13 @@
         <v>3</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
         <v>28</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -1467,10 +1534,10 @@
         <v>0.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
@@ -1485,7 +1552,7 @@
         <v>30</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>28</v>
@@ -1497,7 +1564,7 @@
         <v>27</v>
       </c>
       <c r="AN6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO6" t="n">
         <v>15</v>
@@ -1506,13 +1573,13 @@
         <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
         <v>8</v>
@@ -1524,7 +1591,7 @@
         <v>24</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
@@ -1536,7 +1603,7 @@
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -1649,22 +1716,22 @@
         <v>-5.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH7" t="n">
         <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ7" t="n">
         <v>5</v>
@@ -1715,16 +1782,16 @@
         <v>28</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA7" t="n">
         <v>21</v>
       </c>
       <c r="BB7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" t="n">
         <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.553</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
@@ -1771,49 +1838,49 @@
         <v>39.5</v>
       </c>
       <c r="J8" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="K8" t="n">
         <v>0.472</v>
       </c>
       <c r="L8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M8" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.371</v>
+        <v>0.376</v>
       </c>
       <c r="O8" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="P8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="Q8" t="n">
         <v>0.797</v>
       </c>
       <c r="R8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T8" t="n">
-        <v>39.8</v>
+        <v>39.9</v>
       </c>
       <c r="U8" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="V8" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="W8" t="n">
         <v>9.1</v>
       </c>
       <c r="X8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y8" t="n">
         <v>3.4</v>
@@ -1822,16 +1889,16 @@
         <v>20.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.2</v>
+        <v>104.1</v>
       </c>
       <c r="AC8" t="n">
         <v>1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>10</v>
@@ -1855,37 +1922,37 @@
         <v>4</v>
       </c>
       <c r="AL8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AO8" t="n">
         <v>19</v>
       </c>
       <c r="AP8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
       </c>
       <c r="AR8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS8" t="n">
         <v>27</v>
       </c>
       <c r="AT8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1906,7 +1973,7 @@
         <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" t="n">
         <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>0.489</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
@@ -1953,7 +2020,7 @@
         <v>38.3</v>
       </c>
       <c r="J9" t="n">
-        <v>84.8</v>
+        <v>85</v>
       </c>
       <c r="K9" t="n">
         <v>0.451</v>
@@ -1962,19 +2029,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.363</v>
+        <v>0.362</v>
       </c>
       <c r="O9" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="P9" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="R9" t="n">
         <v>12</v>
@@ -1983,13 +2050,13 @@
         <v>33.5</v>
       </c>
       <c r="T9" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="U9" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V9" t="n">
-        <v>15.1</v>
+        <v>14.8</v>
       </c>
       <c r="W9" t="n">
         <v>7.2</v>
@@ -2001,25 +2068,25 @@
         <v>5.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA9" t="n">
         <v>21.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.6</v>
+        <v>103.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE9" t="n">
         <v>16</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG9" t="n">
         <v>16</v>
@@ -2028,7 +2095,7 @@
         <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AJ9" t="n">
         <v>6</v>
@@ -2046,31 +2113,31 @@
         <v>14</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ9" t="n">
         <v>27</v>
       </c>
       <c r="AR9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
@@ -2082,7 +2149,7 @@
         <v>29</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2207,10 +2274,10 @@
         <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
@@ -2231,7 +2298,7 @@
         <v>17</v>
       </c>
       <c r="AP10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ10" t="n">
         <v>30</v>
@@ -2240,16 +2307,16 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2264,13 +2331,13 @@
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
         <v>17</v>
       </c>
       <c r="BC10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -2299,34 +2366,34 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F11" t="n">
         <v>19</v>
       </c>
       <c r="G11" t="n">
-        <v>0.604</v>
+        <v>0.596</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J11" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="K11" t="n">
-        <v>0.46</v>
+        <v>0.462</v>
       </c>
       <c r="L11" t="n">
         <v>9.4</v>
       </c>
       <c r="M11" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="N11" t="n">
         <v>0.383</v>
@@ -2338,22 +2405,22 @@
         <v>21.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.736</v>
+        <v>0.735</v>
       </c>
       <c r="R11" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S11" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="T11" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="U11" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="V11" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="W11" t="n">
         <v>7.8</v>
@@ -2362,7 +2429,7 @@
         <v>5.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z11" t="n">
         <v>22.2</v>
@@ -2371,13 +2438,13 @@
         <v>19.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.5</v>
+        <v>103.7</v>
       </c>
       <c r="AC11" t="n">
         <v>4.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2392,13 +2459,13 @@
         <v>18</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AJ11" t="n">
         <v>7</v>
       </c>
       <c r="AK11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL11" t="n">
         <v>3</v>
@@ -2419,7 +2486,7 @@
         <v>23</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2434,10 +2501,10 @@
         <v>29</v>
       </c>
       <c r="AW11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2638,7 @@
         <v>7</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
         <v>18</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2777,7 +2844,7 @@
         <v>12</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
         <v>6</v>
@@ -2789,13 +2856,13 @@
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -2938,7 +3005,7 @@
         <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
@@ -2947,16 +3014,16 @@
         <v>6</v>
       </c>
       <c r="AL14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP14" t="n">
         <v>2</v>
@@ -2995,7 +3062,7 @@
         <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -3027,49 +3094,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E15" t="n">
         <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
-        <v>0.34</v>
+        <v>0.348</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J15" t="n">
-        <v>84.2</v>
+        <v>84</v>
       </c>
       <c r="K15" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L15" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M15" t="n">
         <v>24.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.367</v>
+        <v>0.37</v>
       </c>
       <c r="O15" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P15" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.757</v>
+        <v>0.755</v>
       </c>
       <c r="R15" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S15" t="n">
         <v>32.9</v>
@@ -3081,19 +3148,19 @@
         <v>22.5</v>
       </c>
       <c r="V15" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="W15" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y15" t="n">
         <v>4.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA15" t="n">
         <v>19.3</v>
@@ -3102,7 +3169,7 @@
         <v>100.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.6</v>
+        <v>-5.5</v>
       </c>
       <c r="AD15" t="n">
         <v>9</v>
@@ -3111,22 +3178,22 @@
         <v>23</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI15" t="n">
         <v>19</v>
       </c>
       <c r="AJ15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="n">
         <v>5</v>
@@ -3135,7 +3202,7 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AO15" t="n">
         <v>16</v>
@@ -3144,13 +3211,13 @@
         <v>17</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
         <v>20</v>
@@ -3159,13 +3226,13 @@
         <v>11</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
       </c>
       <c r="AX15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY15" t="n">
         <v>13</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>0.556</v>
+        <v>0.545</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3233,13 +3300,13 @@
         <v>0.456</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M16" t="n">
         <v>14.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O16" t="n">
         <v>15.4</v>
@@ -3248,16 +3315,16 @@
         <v>20.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.747</v>
+        <v>0.749</v>
       </c>
       <c r="R16" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S16" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T16" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U16" t="n">
         <v>21.6</v>
@@ -3266,7 +3333,7 @@
         <v>13.4</v>
       </c>
       <c r="W16" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X16" t="n">
         <v>4.5</v>
@@ -3275,19 +3342,19 @@
         <v>5.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3305,7 +3372,7 @@
         <v>16</v>
       </c>
       <c r="AJ16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK16" t="n">
         <v>10</v>
@@ -3329,16 +3396,16 @@
         <v>21</v>
       </c>
       <c r="AR16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS16" t="n">
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AV16" t="n">
         <v>3</v>
@@ -3359,7 +3426,7 @@
         <v>30</v>
       </c>
       <c r="BB16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE17" t="n">
         <v>6</v>
@@ -3481,10 +3548,10 @@
         <v>5</v>
       </c>
       <c r="AH17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3493,13 +3560,13 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM17" t="n">
         <v>14</v>
       </c>
       <c r="AN17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO17" t="n">
         <v>13</v>
@@ -3508,7 +3575,7 @@
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3520,16 +3587,16 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -3573,37 +3640,37 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18" t="n">
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>0.174</v>
+        <v>0.178</v>
       </c>
       <c r="H18" t="n">
         <v>48.8</v>
       </c>
       <c r="I18" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="J18" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.422</v>
+        <v>0.421</v>
       </c>
       <c r="L18" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M18" t="n">
         <v>20.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.343</v>
+        <v>0.34</v>
       </c>
       <c r="O18" t="n">
         <v>14.9</v>
@@ -3612,7 +3679,7 @@
         <v>19.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.751</v>
+        <v>0.756</v>
       </c>
       <c r="R18" t="n">
         <v>11.4</v>
@@ -3642,16 +3709,16 @@
         <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB18" t="n">
-        <v>91.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="AC18" t="n">
         <v>-9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,34 +3730,34 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI18" t="n">
         <v>29</v>
       </c>
       <c r="AJ18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK18" t="n">
         <v>30</v>
       </c>
       <c r="AL18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="n">
         <v>16</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="n">
         <v>29</v>
       </c>
       <c r="AP18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AR18" t="n">
         <v>14</v>
@@ -3708,10 +3775,10 @@
         <v>25</v>
       </c>
       <c r="AW18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY18" t="n">
         <v>19</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" t="n">
         <v>23</v>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.511</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,10 +3840,10 @@
         <v>38.7</v>
       </c>
       <c r="J19" t="n">
-        <v>88.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L19" t="n">
         <v>7.7</v>
@@ -3785,34 +3852,34 @@
         <v>22.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0.344</v>
+        <v>0.346</v>
       </c>
       <c r="O19" t="n">
-        <v>20.7</v>
+        <v>21.1</v>
       </c>
       <c r="P19" t="n">
-        <v>26.5</v>
+        <v>26.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R19" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S19" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T19" t="n">
         <v>45.8</v>
       </c>
       <c r="U19" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V19" t="n">
         <v>13.8</v>
       </c>
       <c r="W19" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X19" t="n">
         <v>3.4</v>
@@ -3821,31 +3888,31 @@
         <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="AB19" t="n">
-        <v>105.8</v>
+        <v>106.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF19" t="n">
         <v>14</v>
       </c>
-      <c r="AF19" t="n">
-        <v>15</v>
-      </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
         <v>9</v>
@@ -3857,16 +3924,16 @@
         <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM19" t="n">
         <v>12</v>
       </c>
       <c r="AN19" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
@@ -3875,22 +3942,22 @@
         <v>4</v>
       </c>
       <c r="AR19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS19" t="n">
         <v>13</v>
       </c>
       <c r="AT19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW19" t="n">
         <v>3</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>5</v>
       </c>
       <c r="AX19" t="n">
         <v>30</v>
@@ -3905,7 +3972,7 @@
         <v>3</v>
       </c>
       <c r="BB19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BC19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4033,7 +4100,7 @@
         <v>13</v>
       </c>
       <c r="AJ20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK20" t="n">
         <v>12</v>
@@ -4051,7 +4118,7 @@
         <v>14</v>
       </c>
       <c r="AP20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ20" t="n">
         <v>11</v>
@@ -4060,7 +4127,7 @@
         <v>4</v>
       </c>
       <c r="AS20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
         <v>18</v>
@@ -4069,7 +4136,7 @@
         <v>15</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
         <v>9</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
@@ -4209,7 +4276,7 @@
         <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4218,7 +4285,7 @@
         <v>14</v>
       </c>
       <c r="AK21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL21" t="n">
         <v>7</v>
@@ -4233,10 +4300,10 @@
         <v>28</v>
       </c>
       <c r="AP21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
@@ -4248,22 +4315,22 @@
         <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY21" t="n">
         <v>5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -4301,46 +4368,46 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E22" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F22" t="n">
         <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>0.792</v>
+        <v>0.787</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>39.3</v>
+        <v>39.1</v>
       </c>
       <c r="J22" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K22" t="n">
-        <v>0.476</v>
+        <v>0.473</v>
       </c>
       <c r="L22" t="n">
         <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O22" t="n">
         <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.804</v>
+        <v>0.803</v>
       </c>
       <c r="R22" t="n">
         <v>11.2</v>
@@ -4349,37 +4416,37 @@
         <v>34.6</v>
       </c>
       <c r="T22" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
       <c r="U22" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V22" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="W22" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Y22" t="n">
         <v>3.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA22" t="n">
         <v>20.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.9</v>
+        <v>105.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4394,10 +4461,10 @@
         <v>25</v>
       </c>
       <c r="AI22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4427,13 +4494,13 @@
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW22" t="n">
         <v>10</v>
@@ -4451,7 +4518,7 @@
         <v>16</v>
       </c>
       <c r="BB22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -4483,58 +4550,58 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F23" t="n">
         <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>0.271</v>
+        <v>0.255</v>
       </c>
       <c r="H23" t="n">
         <v>48.7</v>
       </c>
       <c r="I23" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J23" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.442</v>
+        <v>0.44</v>
       </c>
       <c r="L23" t="n">
         <v>7.1</v>
       </c>
       <c r="M23" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0.346</v>
+        <v>0.345</v>
       </c>
       <c r="O23" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P23" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R23" t="n">
         <v>9.1</v>
       </c>
       <c r="S23" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T23" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U23" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V23" t="n">
         <v>15.1</v>
@@ -4549,19 +4616,19 @@
         <v>6</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="n">
         <v>19</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.7</v>
+        <v>-6.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4576,34 +4643,34 @@
         <v>6</v>
       </c>
       <c r="AI23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ23" t="n">
         <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AL23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM23" t="n">
         <v>17</v>
       </c>
       <c r="AN23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AO23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP23" t="n">
         <v>21</v>
       </c>
-      <c r="AP23" t="n">
-        <v>20</v>
-      </c>
       <c r="AQ23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR23" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AS23" t="n">
         <v>8</v>
@@ -4612,7 +4679,7 @@
         <v>22</v>
       </c>
       <c r="AU23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV23" t="n">
         <v>17</v>
@@ -4621,13 +4688,13 @@
         <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY23" t="n">
         <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
@@ -4636,7 +4703,7 @@
         <v>23</v>
       </c>
       <c r="BC23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G24" t="n">
-        <v>0.319</v>
+        <v>0.326</v>
       </c>
       <c r="H24" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I24" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J24" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L24" t="n">
         <v>6.9</v>
@@ -4695,22 +4762,22 @@
         <v>21.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.316</v>
+        <v>0.317</v>
       </c>
       <c r="O24" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="P24" t="n">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.714</v>
+        <v>0.711</v>
       </c>
       <c r="R24" t="n">
         <v>11.9</v>
       </c>
       <c r="S24" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T24" t="n">
         <v>44.7</v>
@@ -4719,28 +4786,28 @@
         <v>22.6</v>
       </c>
       <c r="V24" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="W24" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="X24" t="n">
         <v>4.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA24" t="n">
         <v>20.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>101.1</v>
+        <v>101.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD24" t="n">
         <v>9</v>
@@ -4761,7 +4828,7 @@
         <v>7</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK24" t="n">
         <v>23</v>
@@ -4776,10 +4843,10 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4791,7 +4858,7 @@
         <v>10</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>3.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF25" t="n">
         <v>8</v>
@@ -4937,7 +5004,7 @@
         <v>8</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI25" t="n">
         <v>8</v>
@@ -4964,13 +5031,13 @@
         <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR25" t="n">
         <v>12</v>
       </c>
       <c r="AS25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT25" t="n">
         <v>14</v>
@@ -4979,7 +5046,7 @@
         <v>30</v>
       </c>
       <c r="AV25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>5</v>
       </c>
       <c r="AD26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -5134,7 +5201,7 @@
         <v>1</v>
       </c>
       <c r="AM26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN26" t="n">
         <v>2</v>
@@ -5149,10 +5216,10 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" t="n">
-        <v>0.326</v>
+        <v>0.333</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J27" t="n">
-        <v>83.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="K27" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L27" t="n">
         <v>6.9</v>
@@ -5247,19 +5314,19 @@
         <v>19.7</v>
       </c>
       <c r="P27" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="R27" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S27" t="n">
         <v>31.6</v>
       </c>
       <c r="T27" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U27" t="n">
         <v>19.9</v>
@@ -5274,34 +5341,34 @@
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z27" t="n">
         <v>23.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AB27" t="n">
         <v>101.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.9</v>
+        <v>-2.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
         <v>26</v>
       </c>
       <c r="AH27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI27" t="n">
         <v>17</v>
@@ -5328,13 +5395,13 @@
         <v>6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR27" t="n">
         <v>7</v>
       </c>
       <c r="AS27" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AT27" t="n">
         <v>12</v>
@@ -5343,10 +5410,10 @@
         <v>27</v>
       </c>
       <c r="AV27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AX27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>7.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5513,7 +5580,7 @@
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS28" t="n">
         <v>7</v>
@@ -5528,10 +5595,10 @@
         <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY28" t="n">
         <v>17</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
         <v>21</v>
       </c>
       <c r="G29" t="n">
-        <v>0.543</v>
+        <v>0.533</v>
       </c>
       <c r="H29" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I29" t="n">
         <v>36</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K29" t="n">
         <v>0.438</v>
@@ -5602,19 +5669,19 @@
         <v>8.4</v>
       </c>
       <c r="M29" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O29" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P29" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.773</v>
+        <v>0.771</v>
       </c>
       <c r="R29" t="n">
         <v>12</v>
@@ -5626,10 +5693,10 @@
         <v>43.6</v>
       </c>
       <c r="U29" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V29" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W29" t="n">
         <v>7</v>
@@ -5638,22 +5705,22 @@
         <v>4.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB29" t="n">
         <v>99.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5665,28 +5732,28 @@
         <v>12</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI29" t="n">
         <v>24</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="n">
         <v>24</v>
       </c>
       <c r="AL29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP29" t="n">
         <v>10</v>
@@ -5704,22 +5771,22 @@
         <v>13</v>
       </c>
       <c r="AU29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA29" t="n">
         <v>6</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -5757,34 +5824,34 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E30" t="n">
         <v>16</v>
       </c>
       <c r="F30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G30" t="n">
-        <v>0.348</v>
+        <v>0.356</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
       </c>
       <c r="I30" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J30" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L30" t="n">
         <v>6.6</v>
       </c>
       <c r="M30" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="N30" t="n">
         <v>0.356</v>
@@ -5796,13 +5863,13 @@
         <v>21.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R30" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S30" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T30" t="n">
         <v>41.6</v>
@@ -5811,13 +5878,13 @@
         <v>20.2</v>
       </c>
       <c r="V30" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W30" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y30" t="n">
         <v>4.9</v>
@@ -5829,13 +5896,13 @@
         <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="AC30" t="n">
         <v>-6.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
@@ -5847,7 +5914,7 @@
         <v>23</v>
       </c>
       <c r="AH30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI30" t="n">
         <v>26</v>
@@ -5874,10 +5941,10 @@
         <v>22</v>
       </c>
       <c r="AQ30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5889,19 +5956,19 @@
         <v>26</v>
       </c>
       <c r="AV30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY30" t="n">
         <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA30" t="n">
         <v>13</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
@@ -6017,16 +6084,16 @@
         <v>-0.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
       </c>
       <c r="AF31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH31" t="n">
         <v>3</v>
@@ -6035,19 +6102,19 @@
         <v>15</v>
       </c>
       <c r="AJ31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK31" t="n">
         <v>17</v>
       </c>
       <c r="AL31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM31" t="n">
         <v>18</v>
       </c>
       <c r="AN31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO31" t="n">
         <v>26</v>
@@ -6065,7 +6132,7 @@
         <v>15</v>
       </c>
       <c r="AT31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU31" t="n">
         <v>8</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-31-2013-14</t>
+          <t>2014-01-31</t>
         </is>
       </c>
     </row>
